--- a/data/seed/portfolio/L-2024-6255/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-6255/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J175"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,237 +535,237 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n">
-        <v>4594000</v>
-      </c>
+      <c r="C8" s="2" t="n">
+        <v>8784000</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2838 01.07.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №32/26</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>41894000</v>
+        <v>28516000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>1194000</v>
+        <v>2440000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omad Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>258457191</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000428996716001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Shartnoma №275/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №29/26 от 03.07.2026</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43088000</v>
+        <v>30956000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>5645000</v>
+        <v>1475000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Guliston Qurilish AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>340059229</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000299776218001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №49/26, QQS 12%</t>
+          <t>Shartnoma №274/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>48733000</v>
+        <v>32431000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46206</v>
+        <v>46208</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>3587000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>260504233</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6255)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>16307000200247247417</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5606 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-6255 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>52320000</v>
+        <v>21931000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>2631000</v>
+        <v>4740000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8310 03.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5764 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>54951000</v>
+        <v>26671000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>2671000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6255)</t>
+          <t>Gulshan Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>345719174</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16307000200247247417</t>
+          <t>20208000899671605001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6255 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за товар по счет-фактуре №6952 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>44451000</v>
+        <v>29342000</v>
       </c>
     </row>
     <row r="14">
@@ -775,432 +775,432 @@
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>8387000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>15415000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>260504233</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №1147 06.07.2026, QQS bilan</t>
+          <t>Iyun oyi uchun ish haqi, reestr №9562</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>52838000</v>
+        <v>13927000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>2617000</v>
+        <v>2911000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shartnoma №178/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8789 07.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>55455000</v>
+        <v>16838000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>1592000</v>
+        <v>2063000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shartnoma №228/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №230/26, НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>57047000</v>
+        <v>18901000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>1211000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>3236000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Durdona Non AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>254735618</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000654826622001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №10/26 от 06.07.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №241/26, QQS bilan</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>58258000</v>
+        <v>15665000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2857000</v>
+        <v>3753000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №221/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №109/26, QQS bilan</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>55401000</v>
+        <v>11912000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>3093000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>22052000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №161/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5458 08.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>52308000</v>
+        <v>33964000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>15415000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>7236000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Namangan Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Shartnoma №283/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>36893000</v>
+        <v>41200000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>16428000</v>
+        <v>1197000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bekobod Oziq-ovqat Savdo MChJ</t>
+          <t>Oqtosh Qurilish MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>243919409</t>
+          <t>360100271</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000253737365001</t>
+          <t>20208000226890086001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №108/26, QQS bilan</t>
+          <t>Ijara haqi iyul oyi uchun, shartnoma №65/25</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20465000</v>
+        <v>40003000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1616000</v>
+        <v>6932000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №192/26, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №5/26</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>18849000</v>
+        <v>33071000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>8259000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>5926000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №40/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3066 09.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10590000</v>
+        <v>38997000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>1897000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Yangi Hayot Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>225659500</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000888696692001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Shartnoma №11/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №234/26</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>12487000</v>
+        <v>36337000</v>
       </c>
     </row>
     <row r="25">
@@ -1210,237 +1210,237 @@
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>6231000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>4218000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2651 09.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №7504</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>18718000</v>
+        <v>32119000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>1197000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>11896000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahor Qurilish MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>318309644</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000591305666001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №21/23</t>
+          <t>Shartnoma №130/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17521000</v>
+        <v>44015000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>12399000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>6225000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №85/26</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №19/26, QQS 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5122000</v>
+        <v>50240000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>2057000</v>
+        <v>5426000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7058</t>
+          <t>Shartnoma №21/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7179000</v>
+        <v>55666000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>1324000</v>
+        <v>3942000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Yog'och MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>301348641</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000507609717001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №760</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1801 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8503000</v>
+        <v>59608000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>1185000</v>
+        <v>2804000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Shartnoma №76/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №47/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>9688000</v>
+        <v>62412000</v>
       </c>
     </row>
     <row r="31">
@@ -1450,37 +1450,37 @@
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>7764000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>3614000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Nurafshon Sut AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>206535209</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000783980085001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Shartnoma №63/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №34/26 от 13.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17452000</v>
+        <v>58798000</v>
       </c>
     </row>
     <row r="32">
@@ -1490,223 +1490,223 @@
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>5358000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>6993000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №205 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №3845</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>22810000</v>
+        <v>51805000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>4766000</v>
+        <v>1335000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Shartnoma №175/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, h/f №2976 14.07.2026,QQS bilan</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>27576000</v>
+        <v>53140000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>1830000</v>
+        <v>1374000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3442</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9092 15.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>29406000</v>
+        <v>54514000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>2274000</v>
+        <v>2102000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Guliston Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>227842929</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000717290101001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №27/26</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>27132000</v>
+        <v>52412000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>3554000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>2102000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №44/26, QQS 12%</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>30686000</v>
+        <v>50310000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>1793000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>2910000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1716,37 +1716,37 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №124/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №152/26</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>32479000</v>
+        <v>47400000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>1576000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>8637000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1756,131 +1756,131 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №10/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №2823</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>34055000</v>
+        <v>38763000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>2102000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>2233000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kamalak Savdo MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>384292917</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000729010114001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IYUN OYI UCHUN IJTIMOIY SOLIQ</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8111</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>31953000</v>
+        <v>40996000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>2102000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>2066000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Shartnoma №299/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>29851000</v>
+        <v>43062000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>4659000</v>
+        <v>2254000</v>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Kattaqo'rg'on Metall MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>287912416</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000563073741001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7526</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №218/26</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>25192000</v>
+        <v>40808000</v>
       </c>
     </row>
     <row r="42">
@@ -1892,35 +1892,35 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>930000</v>
+        <v>5471000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8837</t>
+          <t>SHARTNOMA №272/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>26122000</v>
+        <v>46279000</v>
       </c>
     </row>
     <row r="43">
@@ -1931,36 +1931,36 @@
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>4230000</v>
+        <v>15062000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Nurafshon Sut AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206535209</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000783980085001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'ov, shartnoma №214/26</t>
+          <t>Предоплата за материалы по договору №225/26</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21892000</v>
+        <v>31217000</v>
       </c>
     </row>
     <row r="44">
@@ -1972,35 +1972,35 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>20734000</v>
+        <v>12095000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Shartnoma №48/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №19/26, НДС 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>42626000</v>
+        <v>43312000</v>
       </c>
     </row>
     <row r="45">
@@ -2012,35 +2012,35 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>993000</v>
+        <v>11444000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №81/26 от 20.07.2026</t>
+          <t>Оплата по с/ф №3620 за поставленный товар</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>43619000</v>
+        <v>54756000</v>
       </c>
     </row>
     <row r="46">
@@ -2050,37 +2050,37 @@
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>6733000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>3476000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bekobod Oziq-ovqat Savdo MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>243919409</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000253737365001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1155</t>
+          <t>Оплата за товар по с/ф №3835 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>36886000</v>
+        <v>58232000</v>
       </c>
     </row>
     <row r="47">
@@ -2090,23 +2090,23 @@
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>9669000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>1664000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sarbon Avto Savdo XK</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>311066769</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000080498772001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2116,451 +2116,451 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №163/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №13/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>27217000</v>
+        <v>59896000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>1439000</v>
+        <v>1585000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toshkent Yog'och MChJ</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>393485429</t>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000550929361001</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hiso-faktura №4491 21.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №194 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28656000</v>
+        <v>61481000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>5779000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>1385000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №200/26 от 21.07.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2353 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22877000</v>
+        <v>62866000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>34918000</v>
+        <v>3379000</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №182/26, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №8716</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>-12041000</v>
+        <v>59487000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>1326000</v>
+        <v>5702000</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №295/26</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №105/26</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>-13367000</v>
+        <v>53785000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1969000</v>
+        <v>6876000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Оплата за транспортные услуги по договору №233/26</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>-15336000</v>
+        <v>46909000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>6891000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>16233000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №234/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5642 22.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>-22227000</v>
+        <v>63142000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>2730000</v>
+        <v>1385000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1137 от 24.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №922</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>-19497000</v>
+        <v>64527000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>2075000</v>
+        <v>3150000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №89/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6164</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>-17422000</v>
+        <v>67677000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>8454000</v>
+        <v>1634000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №190/26 ОТ 27.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartn. №113/26, QQS 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>-8968000</v>
+        <v>69311000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>3106000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3381</t>
+          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА ИЮНЬ</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>-5862000</v>
+        <v>67311000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>2582000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>11395000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Yog'och MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>301348641</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000507609717001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3616</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №261/26</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>-3280000</v>
+        <v>55916000</v>
       </c>
     </row>
     <row r="59">
@@ -2570,23 +2570,23 @@
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>748000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>5948000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000781229154001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2596,446 +2596,446 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №289/26, QQS 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>-4028000</v>
+        <v>61864000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>1896000</v>
+        <v>5924000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Omad Meva Eksport MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>258457191</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000428996716001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2256</t>
+          <t>Оплата за продукцию по договору №203/26, НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>-2132000</v>
+        <v>67788000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>1030000</v>
+        <v>2528000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №223/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8986</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>-1102000</v>
+        <v>70316000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>1103000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>2166000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №141/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7774</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>-2205000</v>
+        <v>72482000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>47283000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>748000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000782768579001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №236 30.07.2026, QQS bilan</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>45078000</v>
+        <v>71734000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>300000</v>
+        <v>3408000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Angren Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №7/26</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>44778000</v>
+        <v>68326000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>1921000</v>
+        <v>3468000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Nurafshon Sut AJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206535209</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000783980085001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №29/26, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №231/26</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>42857000</v>
+        <v>64858000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>5130000</v>
+        <v>3928000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7765</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №197/26</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>37727000</v>
+        <v>60930000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>20664000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>5718000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Toshkent Yog'och MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>393485429</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000550929361001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №24/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №43/26</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>58391000</v>
+        <v>55212000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>10789000</v>
+        <v>1747000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Andijon Metall Servis XK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>316459876</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000329073036001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4444</t>
+          <t>Предоплата за товар по договору №76/26 от 30.07.2026</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>69180000</v>
+        <v>56959000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>6500000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>297400592</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2489 03.08.2026, QQS bilan</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>75680000</v>
+        <v>56659000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>6406000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>16215000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Yangi Hayot Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>225659500</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000888696692001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №4/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>82086000</v>
+        <v>40444000</v>
       </c>
     </row>
     <row r="71">
@@ -3047,35 +3047,35 @@
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>4299000</v>
+        <v>13709000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7680 03.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №88/26, QQS 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>86385000</v>
+        <v>54153000</v>
       </c>
     </row>
     <row r="72">
@@ -3087,35 +3087,35 @@
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>4023000</v>
+        <v>6127000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №125/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №8383 за поставленный товар</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>90408000</v>
+        <v>60280000</v>
       </c>
     </row>
     <row r="73">
@@ -3125,37 +3125,37 @@
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>9739000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>2274000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och XK</t>
+          <t>Kamalak Savdo MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>233510845</t>
+          <t>384292917</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000165571647001</t>
+          <t>20208000729010114001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №4/26, QQS BILAN</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №161/26, QQS 12%</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>80669000</v>
+        <v>62554000</v>
       </c>
     </row>
     <row r="74">
@@ -3165,333 +3165,333 @@
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>20014000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>1627000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №182/26</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №3152 03.08.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>60655000</v>
+        <v>64181000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>3607000</v>
+        <v>1052000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Yog'och MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>301348641</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000507609717001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Shartnoma №95/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №279/26, QQS 12%</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>64262000</v>
+        <v>65233000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>1778000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>1432000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Durdona Non AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>254735618</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000654826622001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3572</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №92/26</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>66040000</v>
+        <v>63801000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>10500000</v>
+        <v>32634000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6255)</t>
+          <t>Chirchiq Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>16307000200247247417</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6255 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за сырье по дог. №166/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>55540000</v>
+        <v>31167000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>16225000</v>
+        <v>8558000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Angren Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №164/26</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>39315000</v>
+        <v>22609000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1260000</v>
+        <v>10500000</v>
       </c>
       <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bahor Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>318309644</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6255)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000591305666001</t>
+          <t>16307000200247247417</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartnoma №21/23</t>
+          <t>Kredit shartnomasi L-2024-6255 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>38055000</v>
+        <v>12109000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>8714000</v>
+        <v>2330000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Shartnoma №78/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №66/26, НДС 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46769000</v>
+        <v>14439000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>3738000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>1351000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Nurafshon Sut AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>206535209</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000783980085001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №5619</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №139/26, QQS bilan</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>50507000</v>
+        <v>13088000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>46918000</v>
+        <v>16225000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Farg'ona Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>348919504</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000806499999001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3501,637 +3501,637 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №202/26</t>
+          <t>Перечисление заработной платы за июль 2026 г. сгласно реестру №6604</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>3589000</v>
+        <v>-3137000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>812000</v>
+        <v>17472000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Tong Moy AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>248542935</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000092936148001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8638 11.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №124 за поставленный товар</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>4401000</v>
+        <v>14335000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>904000</v>
+        <v>5789000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Chust Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>235107089</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000061619563001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Shartnoma №230/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7375 07.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>5305000</v>
+        <v>20124000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>16069000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>3264000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och XK</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>233510845</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000165571647001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №187/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №7040 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>-10764000</v>
+        <v>23388000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>684000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Oqtosh Qurilish MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>360100271</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000226890086001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №225/26, QQS 12%</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>-10080000</v>
+        <v>22128000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>3074000</v>
+        <v>23883000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Gulshan Mato MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>345719174</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000899671605001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Shartnoma №195/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №110 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>-7006000</v>
+        <v>46011000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>731000</v>
+        <v>9305000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>391950468</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000649999987001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9851 14.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №244/26, QQS 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>-6275000</v>
+        <v>55316000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>6196000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>2036000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bekobod Oziq-ovqat Savdo MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>243919409</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000253737365001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2049</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9651</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>-12471000</v>
+        <v>57352000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>2078000</v>
+        <v>1716000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата з продукцию по договору №264/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №104/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>-10393000</v>
+        <v>59068000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>1580000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>2244000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Yog'och MChJ</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>301348641</t>
+          <t>293595692</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000507609717001</t>
+          <t>20208000419910329001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Shartnoma №18/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №174/26</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>-8813000</v>
+        <v>56824000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>2212000</v>
+        <v>5800000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №287/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>-11025000</v>
+        <v>51024000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>2212000</v>
+        <v>11706000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I IYUL 2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №255/26</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>-13237000</v>
+        <v>39318000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>14589000</v>
+        <v>17333000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №217/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №253/26, QQS bilan</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>-27826000</v>
+        <v>21985000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46253</v>
+        <v>46245</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>1686000</v>
+        <v>2047000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7149 19.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №181/26, QQS 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>-26140000</v>
+        <v>24032000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>1648000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>6476000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1845 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №2536</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>-24492000</v>
+        <v>17556000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46254</v>
+        <v>46246</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>780000</v>
+        <v>2294000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Shartnoma №39/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №197/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>-23712000</v>
+        <v>19850000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46255</v>
+        <v>46246</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>2526000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>2241000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4141,197 +4141,197 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Shartnoma №40/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №145/26</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>-21186000</v>
+        <v>17609000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>767000</v>
+        <v>2575000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Shartnoma №62/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1004 13.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>-20419000</v>
+        <v>20184000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>9506000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>2382000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Andijon Metall Servis XK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>316459876</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000329073036001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8773</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9972 13.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>-29925000</v>
+        <v>22566000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>7089000</v>
+        <v>14866000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Yog'och MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>301348641</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000507609717001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1676 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №9114 за поставленный товар</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>-22836000</v>
+        <v>37432000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>6119000</v>
+        <v>2936000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5585 24.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4832</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>-16717000</v>
+        <v>40368000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>3001000</v>
+        <v>2776000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Gulshan Mato MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>345719174</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000899671605001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4341,117 +4341,117 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5417 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №245/26, QQS 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>-13716000</v>
+        <v>43144000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>2052000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>2212000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Shartnoma №1/26 bo'yicha oldindan to'lov</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>-11664000</v>
+        <v>40932000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>1903000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>2212000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7105 24.08.2026, QQS bilan</t>
+          <t>JSHDS IYUL OYI UCHUN</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>-9761000</v>
+        <v>38720000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>856000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>4265000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4461,37 +4461,37 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2610 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №173/26</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>-8905000</v>
+        <v>34455000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>788000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>3733000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000781229154001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4501,672 +4501,677 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun o'lov avgust</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7254 19.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>-9693000</v>
+        <v>38188000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2007000</v>
+        <v>5626000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №148/26</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>-11700000</v>
+        <v>32562000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46259</v>
+        <v>46254</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>745000</v>
+        <v>4283000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Olmaliq Metall Servis MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>248730025</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000538553602001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5779 25.08.2026, QQS bilan</t>
+          <t>Shartnoma №90/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>-10955000</v>
+        <v>36845000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46259</v>
+        <v>46254</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>12458000</v>
+        <v>4021000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Guliston Yog' Zavodi MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>227842929</t>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000717290101001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №95/26</t>
+          <t>Tovarlar uchun to'lov h/f №1561</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>-23413000</v>
+        <v>32824000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46260</v>
+        <v>46255</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>26486000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>1477000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9856 26.08.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №4558</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>3073000</v>
+        <v>31347000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46260</v>
+        <v>46255</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>702000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>2044000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №7521 26.08.2026, QQS BILAN</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>3775000</v>
+        <v>29303000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>702000</v>
+        <v>4458000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7158</t>
+          <t>Shartnoma №187/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>4477000</v>
+        <v>33761000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>673000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>788000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000782768579001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №213/26, QQS 12%</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>5150000</v>
+        <v>32973000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46262</v>
+        <v>46258</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>13456000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>5107000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Afrosiyob Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>291940952</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000373736524001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2405 28.08.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №244/26</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>18606000</v>
+        <v>27866000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>8351000</v>
+        <v>3376000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Toshkent Yog'och MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>393485429</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000550929361001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5597 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №2570 за поставленный товар</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>26957000</v>
+        <v>31242000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>2395000</v>
+        <v>11096000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2917 31.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №195/26, QQS 12%</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>29352000</v>
+        <v>42338000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>2184000</v>
+        <v>2970000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Sarbon Non MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>373002595</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000855360203001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3677 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6416</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>31536000</v>
+        <v>45308000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>1827000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>18112000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Yog'och MChJ</t>
+          <t>Nurafshon Sut AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>301348641</t>
+          <t>206535209</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000507609717001</t>
+          <t>20208000783980085001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3941</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №6075</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>33363000</v>
+        <v>27196000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>950000</v>
+        <v>1280000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5050 31.08.2026, QQSbilan</t>
+          <t>Оплата по счет-фактуре №6251 за поставленный товар</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>34313000</v>
+        <v>28476000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>300000</v>
+        <v>1384000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Angren Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №92/26, QQS bilan</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>34013000</v>
+        <v>27092000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>2651000</v>
+        <v>2250000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Yog'och MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>301348641</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000507609717001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9751</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1766</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>36664000</v>
+        <v>29342000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46267</v>
+        <v>46262</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>1400000</v>
+        <v>1684000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Shartnoma №256/26 bo'yicha oldindan to'lov</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №131</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>38064000</v>
+        <v>31026000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>2026000</v>
+        <v>4922000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Chust Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>235107089</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000061619563001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5176,587 +5181,587 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3030 03.09.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4778</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>40090000</v>
+        <v>35948000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>16351000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>3135000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Namangan Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №6901</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9300</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>23739000</v>
+        <v>39083000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46270</v>
+        <v>46265</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>3016000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6255)</t>
+          <t>Saodat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>16307000200247247417</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6255 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №275/26, QQS 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>13239000</v>
+        <v>42099000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>11334000</v>
+        <v>2587000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Shartnoma №260/6 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №256/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>24573000</v>
+        <v>44686000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>3099000</v>
+        <v>1116000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov,hisob-faktura №8185 07.09.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №8120 за поставленный товар</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>27672000</v>
+        <v>45802000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>2963000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>260504233</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Shartnoma №80/26 bo'yicha oldindan to'lov</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>30635000</v>
+        <v>45502000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>1270000</v>
+        <v>5573000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bahor Qurilish MChJ</t>
+          <t>Nurafshon Sut AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>318309644</t>
+          <t>206535209</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000591305666001</t>
+          <t>20208000783980085001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №21/23</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №54/26, QQS bilan</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>29365000</v>
+        <v>39929000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>7040000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>1665000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3703 09.09.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №158/26, QQS bilan</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>36405000</v>
+        <v>38264000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>4850000</v>
+        <v>4619000</v>
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9870</t>
+          <t>Tovarlar uchun to'lov h/f №381</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>31555000</v>
+        <v>33645000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>11423000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>547000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och XK</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>233510845</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000165571647001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №29/26</t>
+          <t>SHARTNOMA №57/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>20132000</v>
+        <v>34192000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>1510000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>3883000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Shartnoma №164/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartn. №22/26, QQS bilan</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>21642000</v>
+        <v>30309000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>2570000</v>
+        <v>6054000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Nurafshon Sut AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206535209</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000783980085001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №22/26</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №59/26 ОТ 03.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>19072000</v>
+        <v>24255000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>4205000</v>
+        <v>13381000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №180/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №35/26, QQS bilan</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>14867000</v>
+        <v>10874000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>1051000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>306005158</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6255)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>16307000200247247417</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4771</t>
+          <t>Kredit shartnomasi L-2024-6255 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>15918000</v>
+        <v>374000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>72581000</v>
+        <v>350000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Chust Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>235107089</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000061619563001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №159/26, QQS 12%</t>
+          <t>Shartnoma №14/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>88499000</v>
+        <v>724000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>2751000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>5170000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5766,197 +5771,192 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shartnoma №296/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №5070</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>91250000</v>
+        <v>-4446000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>1731000</v>
+        <v>16351000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Guliston Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>227842929</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000717290101001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №3113</t>
+          <t>Avgust oyi uchun ish haqi, reestr №4650</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>89519000</v>
+        <v>-20797000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>3359000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>16373000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №26/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №193/26, QQS bilan</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>92878000</v>
+        <v>-37170000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46280</v>
+        <v>46274</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>1707000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>1270000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Oqtosh Qurilish MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>360100271</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000226890086001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №54/26, QQS 12%</t>
+          <t>Ijara haqi sentyabr oyi uchun, shartnoma №65/25</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>94585000</v>
+        <v>-38440000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>5997000</v>
+        <v>482000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Omad Meva Eksport MChJ</t>
+          <t>Chust Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>258457191</t>
+          <t>235107089</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000428996716001</t>
+          <t>20208000061619563001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №166/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №178/26, QQS 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>100582000</v>
+        <v>-37958000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>1125000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>3259000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5966,757 +5966,757 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9387 16.09.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №186/26, QQS bilan</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>101707000</v>
+        <v>-41217000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>2230000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>2619000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №159/26, QQS 12%</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>99477000</v>
+        <v>-38598000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>2230000</v>
+        <v>3010000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Tovarlar uchun to'lov h/f №5879</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>97247000</v>
+        <v>-41608000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>1713000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>3042000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №96/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №5303</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>98960000</v>
+        <v>-44650000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>1500000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>5348000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Afrosiyob Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>291940952</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000373736524001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1153 от 17.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №98/26, QQS bilan</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>100460000</v>
+        <v>-49998000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>1101000</v>
+        <v>569000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Shartnoma №247/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №164/26 от 15.09.2026</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>101561000</v>
+        <v>-49429000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>14864000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>1258000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7973</t>
+          <t>Tovarlar uchun to'lov h/f №3206</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>116425000</v>
+        <v>-50687000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>1789000</v>
+        <v>10814000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Bekobod Oziq-ovqat Savdo MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>243919409</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000253737365001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2018</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №1/26</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>114636000</v>
+        <v>-61501000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>10086000</v>
+        <v>278000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Omad Meva Eksport MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>258457191</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000428996716001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mahsulot uchunto'lov, shartn. №286/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №9387 16.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>124722000</v>
+        <v>-61223000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>2116000</v>
-      </c>
+      <c r="C153" s="2" t="n">
+        <v>2230000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Olmaliq Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>248730025</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000538553602001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №111/26, QQS 12%</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>126838000</v>
+        <v>-63453000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>1572000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>2230000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №17/26 от 21.9.2026</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>128410000</v>
+        <v>-65683000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>2070000</v>
+        <v>2328000</v>
       </c>
       <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №160/26</t>
+          <t>Tovarlar uchun to'lov h/f №9894</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>126340000</v>
+        <v>-68011000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>2161000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>2620000</v>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>QQS AVGUST 2026 UCHUN</t>
+          <t>Shartnoma №247/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>124179000</v>
+        <v>-65391000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>2828000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>1833000</v>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bekobod Oziq-ovqat Savdo MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>243919409</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000253737365001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №258/26, QQS bilan</t>
+          <t>Shartnoma №2/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>121351000</v>
+        <v>-63558000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>3018000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>459000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Farg'ona Oziq-ovqat Savdo MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>348919504</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000806499999001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9850</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5252 18.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>118333000</v>
+        <v>-63099000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>6706000</v>
-      </c>
+      <c r="C159" s="2" t="n">
+        <v>1108000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Chirchiq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>206676930</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000049877238001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Yetkazilgan ovar uchun to'lov h/f №7910</t>
+          <t>Tovarlar uchun to'lov h/f №2785</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>125039000</v>
+        <v>-64207000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
-      <c r="C160" s="2" t="n">
-        <v>3269000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>1327000</v>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Guliston Yog' Zavodi MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>227842929</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000717290101001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9595</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №850</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>121770000</v>
+        <v>-62880000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
-      <c r="C161" s="2" t="n">
-        <v>63079000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>1263000</v>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Farg'ona Oziq-ovqat Savdo MChJ</t>
+          <t>Chust Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>348919504</t>
+          <t>235107089</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000806499999001</t>
+          <t>20208000061619563001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №296/26</t>
+          <t>Оплата за товар по с/ф №3031 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>58691000</v>
+        <v>-61617000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="n">
-        <v>8301000</v>
+        <v>586000</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>SHARTNOMA №161/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6500 21.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>66992000</v>
+        <v>-61031000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
-      <c r="C163" s="2" t="n">
-        <v>794000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>266000</v>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000781229154001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6726,317 +6726,317 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Предоплата за товар по дог. №17/26 от 21.9.2026</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>66198000</v>
+        <v>-60765000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>6611000</v>
+        <v>2087000</v>
       </c>
       <c r="D164" s="2" t="n"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bunyodkor Sut Mahsulotlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>224351070</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000990616195001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №211/26</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>59587000</v>
+        <v>-62852000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>2316000</v>
-      </c>
+      <c r="C165" s="2" t="n">
+        <v>5875000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>369452544</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000881024304001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Shartnoma №293/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №7815</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>61903000</v>
+        <v>-68727000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
       <c r="C166" s="2" t="n"/>
       <c r="D166" s="2" t="n">
-        <v>2003000</v>
+        <v>138965000</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Shartnoma №14/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №188/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>63906000</v>
+        <v>70238000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46294</v>
+        <v>46287</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
       <c r="C167" s="2" t="n"/>
       <c r="D167" s="2" t="n">
-        <v>2302000</v>
+        <v>249000</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7611 за поставленный товар</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1859</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>66208000</v>
+        <v>70487000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46294</v>
+        <v>46287</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
-      <c r="C168" s="2" t="n">
-        <v>26418000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>246000</v>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №178/26</t>
+          <t>Shartnoma №209/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>39790000</v>
+        <v>70733000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="n">
-        <v>2903000</v>
+        <v>6106000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sharq Meva-Sabzavot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>306005158</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000554593801001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4681 30.09.2026, QQS bilan</t>
+          <t>Yetkazilgan ovar uchun to'lov h/f №7910</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>42693000</v>
+        <v>76839000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B170" t="n">
         <v>262</v>
       </c>
       <c r="C170" s="2" t="n"/>
       <c r="D170" s="2" t="n">
-        <v>1033000</v>
+        <v>908000</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Yulduz Mebel XK</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>297400592</t>
+          <t>250423313</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>20208000942997762001</t>
+          <t>20208000341697652001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №191/26, НДС 12%</t>
+          <t>Shartnoma №159/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>43726000</v>
+        <v>77747000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B171" t="n">
         <v>263</v>
       </c>
       <c r="C171" s="2" t="n"/>
       <c r="D171" s="2" t="n">
-        <v>969000</v>
+        <v>446000</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport MChJ</t>
+          <t>Gulshan Mato MChJ</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>260504233</t>
+          <t>345719174</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20208000343416976001</t>
+          <t>20208000899671605001</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7046,111 +7046,511 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5960 от 30.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3651 23.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>44695000</v>
+        <v>78193000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B172" t="n">
         <v>264</v>
       </c>
-      <c r="C172" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>998000</v>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>234864115</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000760971762001</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6024 25.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>44395000</v>
+        <v>79191000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B173" t="n">
         <v>265</v>
       </c>
-      <c r="C173" s="2" t="n">
-        <v>2595000</v>
-      </c>
-      <c r="D173" s="2" t="n"/>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>855000</v>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel MChJ</t>
+          <t>Saodat Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>279164598</t>
+          <t>300515895</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>20208000603290730001</t>
+          <t>20208000459380109001</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Shartnoma №113/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>80046000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B174" t="n">
+        <v>266</v>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>412000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Namangan Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>250423313</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000341697652001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Shartnoma №293/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>80458000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B175" t="n">
+        <v>267</v>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>452000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Namangan Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>250423313</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000341697652001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Shartnoma №250/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>80910000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B176" t="n">
+        <v>268</v>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>794000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000782768579001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>80116000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B177" t="n">
+        <v>269</v>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>2395000</v>
+      </c>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Ziyo Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>293595692</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000419910329001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
           <t>01089</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartn. №229/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n">
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartn. №1/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>77721000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B178" t="n">
+        <v>270</v>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>46725000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Chirchiq Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>206676930</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000049877238001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №5253</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>30996000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B179" t="n">
+        <v>271</v>
+      </c>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n">
+        <v>8826000</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Saodat Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>300515895</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20208000459380109001</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, h/f №7772 30.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>39822000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B180" t="n">
+        <v>272</v>
+      </c>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n">
+        <v>1466000</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Namangan Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>250423313</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000341697652001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №5960 от 30.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>41288000</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B181" t="n">
+        <v>273</v>
+      </c>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n">
+        <v>463000</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Namangan Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>250423313</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20208000341697652001</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9544</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>41751000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B182" t="n">
+        <v>274</v>
+      </c>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n">
+        <v>349000</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Namangan Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>250423313</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>20208000341697652001</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1758</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>42100000</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B183" t="n">
+        <v>275</v>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Yangi Asr Bank</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Hisob-kassa xizmati uchun haq</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
         <v>41800000</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C174" s="4" t="n">
-        <v>506903000</v>
-      </c>
-      <c r="D174" s="4" t="n">
-        <v>511403000</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="C184" s="4" t="n">
+        <v>506456000</v>
+      </c>
+      <c r="D184" s="4" t="n">
+        <v>510956000</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C175" s="4" t="n">
+      <c r="C185" s="4" t="n">
         <v>41800000</v>
       </c>
-      <c r="D175" s="4" t="n"/>
+      <c r="D185" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
